--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:15:02+00:00</t>
+    <t>2026-02-06T13:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T13:40:54+00:00</t>
+    <t>2026-02-06T14:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T15:19:47+00:00</t>
+    <t>2026-02-25T14:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T14:12:38+00:00</t>
+    <t>2026-02-26T10:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:50:19+00:00</t>
+    <t>2026-02-26T16:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -123,25 +123,34 @@
     <t>Count</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
     <t>SEJ</t>
   </si>
   <si>
     <t>Identifiant du séjour</t>
+  </si>
+  <si>
+    <t>NUMDOSS</t>
+  </si>
+  <si>
+    <t>Numéro de dossier administratif du séjour</t>
   </si>
 </sst>
 </file>
@@ -451,7 +460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -470,15 +479,27 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="B3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="D3" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:06:51+00:00</t>
+    <t>2026-02-27T10:48:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:48:32+00:00</t>
+    <t>2026-02-27T17:34:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T17:34:14+00:00</t>
+    <t>2026-03-02T09:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T09:04:22+00:00</t>
+    <t>2026-03-02T10:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:45:03+00:00</t>
+    <t>2026-03-02T11:00:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T11:00:56+00:00</t>
+    <t>2026-03-16T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:16:38+00:00</t>
+    <t>2026-03-16T15:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:31:45+00:00</t>
+    <t>2026-03-17T17:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T17:41:27+00:00</t>
+    <t>2026-04-09T09:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:33:58+00:00</t>
+    <t>2026-05-07T09:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T09:37:23+00:00</t>
+    <t>2026-06-10T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T13:07:20+00:00</t>
+    <t>2026-06-16T08:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:06:32+00:00</t>
+    <t>2026-06-16T08:52:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:52:34+00:00</t>
+    <t>2026-06-16T09:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T09:33:33+00:00</t>
+    <t>2026-06-16T10:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:35:13+00:00</t>
+    <t>2026-06-16T10:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:46:14+00:00</t>
+    <t>2026-06-16T11:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:08:56+00:00</t>
+    <t>2026-06-16T14:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:39:41+00:00</t>
+    <t>2026-06-16T16:50:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:50:35+00:00</t>
+    <t>2026-06-17T09:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:02:27+00:00</t>
+    <t>2026-06-17T09:20:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:20:14+00:00</t>
+    <t>2026-06-29T13:11:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:11:00+00:00</t>
+    <t>2026-06-30T08:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:27:53+00:00</t>
+    <t>2026-06-30T13:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:41:45+00:00</t>
+    <t>2026-06-30T14:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:01:12+00:00</t>
+    <t>2026-06-30T14:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:55:37+00:00</t>
+    <t>2026-07-01T09:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T09:47:49+00:00</t>
+    <t>2026-07-01T11:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:47:31+00:00</t>
+    <t>2026-07-01T13:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:17:54+00:00</t>
+    <t>2026-07-01T14:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:33:44+00:00</t>
+    <t>2026-07-01T14:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:55:22+00:00</t>
+    <t>2026-07-01T15:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:33:30+00:00</t>
+    <t>2026-07-20T07:42:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:42:46+00:00</t>
+    <t>2026-07-22T13:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
+++ b/main/ig/CodeSystem-tddui-encounter-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:04:03+00:00</t>
+    <t>2026-07-22T14:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
